--- a/bills/JXZFSP01/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP01/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/13 16:30:00</t>
+          <t>09/15 11:33:43</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.55</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>17283.95</t>
+          <t>25730.99</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>yxhgq79</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -117,12 +117,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08/11 14:11:45</t>
+          <t>08/13 16:30:00</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>90000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -132,12 +132,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>10975.61</t>
+          <t>17283.95</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -159,12 +159,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08/10 14:50:45</t>
+          <t>08/11 14:11:45</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1020000</t>
+          <t>90000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -174,12 +174,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7.85</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>129936.31</t>
+          <t>10975.61</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -201,12 +201,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08/07 20:48:29</t>
+          <t>08/10 14:50:45</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>1020000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -216,12 +216,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>7.85</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>31645.57</t>
+          <t>129936.31</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -243,7 +243,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08/07 13:36:26</t>
+          <t>08/07 20:48:29</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -258,12 +258,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>30864.2</t>
+          <t>31645.57</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -285,12 +285,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08/07 10:14:02</t>
+          <t>08/07 13:36:26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -300,12 +300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7.95</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>37735.85</t>
+          <t>30864.2</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -327,12 +327,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08/04 15:44:12</t>
+          <t>08/07 10:14:02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -342,12 +342,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.95</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>12500</t>
+          <t>37735.85</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -369,7 +369,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>08/04 13:42:03</t>
+          <t>08/04 15:44:12</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -384,12 +384,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>12500</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -411,12 +411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07/31 20:07:18</t>
+          <t>08/04 13:42:03</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -426,12 +426,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>18750</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -453,12 +453,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07/31 14:54:55</t>
+          <t>07/31 20:07:18</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>350000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -468,12 +468,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>7.95</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>44025.16</t>
+          <t>18750</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -495,12 +495,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07/31 14:43:55</t>
+          <t>07/31 14:54:55</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>350000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -510,12 +510,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>7.95</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>20987.65</t>
+          <t>44025.16</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -537,12 +537,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07/29 20:09:55</t>
+          <t>07/31 14:43:55</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>185000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>22699.39</t>
+          <t>20987.65</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -579,12 +579,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07/28 12:19:44</t>
+          <t>07/29 20:09:55</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>185000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>22699.39</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -621,12 +621,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07/27 10:20:29</t>
+          <t>07/28 12:19:44</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>290000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>36024.84</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>yxhgq79</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -663,12 +663,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07/26 12:04:38</t>
+          <t>07/27 10:20:29</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>290000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>36024.84</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>yxhgq79</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -705,7 +705,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07/25 14:40:44</t>
+          <t>07/26 12:04:38</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -747,12 +747,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07/24 11:18:18</t>
+          <t>07/25 14:40:44</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>170000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -762,12 +762,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>7.95</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>21383.65</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -789,12 +789,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07/24 10:09:54</t>
+          <t>07/24 11:18:18</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>130000</t>
+          <t>170000</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -804,12 +804,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>7.95</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>15662.65</t>
+          <t>21383.65</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -831,12 +831,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07/23 10:46:36</t>
+          <t>07/24 10:09:54</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>130000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>30864.2</t>
+          <t>15662.65</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -873,12 +873,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07/23 10:04:03</t>
+          <t>07/23 10:46:36</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>7.95</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>50314.47</t>
+          <t>30864.2</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -915,12 +915,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07/23 09:57:25</t>
+          <t>07/23 10:04:03</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>420000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.95</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>52500</t>
+          <t>50314.47</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -957,12 +957,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07/22 14:50:27</t>
+          <t>07/23 09:57:25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>80000</t>
+          <t>420000</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>9638.55</t>
+          <t>52500</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -999,12 +999,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07/22 14:46:31</t>
+          <t>07/22 14:50:27</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>274950</t>
+          <t>80000</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>33530.49</t>
+          <t>9638.55</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07/22 10:20:48</t>
+          <t>07/22 14:46:31</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>274950</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>7.95</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>25157.23</t>
+          <t>33530.49</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07/21 14:22:59</t>
+          <t>07/22 10:20:48</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>7.95</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>25157.23</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1125,12 +1125,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07/20 13:58:56</t>
+          <t>07/21 14:22:59</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>7361.96</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1167,12 +1167,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07/19 19:17:33</t>
+          <t>07/20 13:58:56</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>7361.96</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1209,12 +1209,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07/17 18:38:51</t>
+          <t>07/19 19:17:33</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>46250</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1251,12 +1251,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07/17 18:14:47</t>
+          <t>07/17 18:38:51</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>183843</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>22557.42</t>
+          <t>46250</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1293,12 +1293,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07/17 17:10:27</t>
+          <t>07/17 18:14:47</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>183843</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>22557.42</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1335,12 +1335,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07/17 15:25:18</t>
+          <t>07/17 17:10:27</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1377,12 +1377,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07/17 10:45:36</t>
+          <t>07/17 15:25:18</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>120989</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1392,12 +1392,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>8.85</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>13671.07</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1419,12 +1419,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07/16 12:19:58</t>
+          <t>07/17 10:45:36</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>220000</t>
+          <t>120989</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.85</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>26190.48</t>
+          <t>13671.07</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1461,12 +1461,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07/15 19:20:32</t>
+          <t>07/16 12:19:58</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>62500</t>
+          <t>26190.48</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07/15 16:22:26</t>
+          <t>07/15 19:20:32</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1518,12 +1518,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>13496.93</t>
+          <t>62500</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1545,12 +1545,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07/14 19:36:11</t>
+          <t>07/15 16:22:26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>110000</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>28395.06</t>
+          <t>13496.93</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1587,12 +1587,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07/13 13:36:47</t>
+          <t>07/14 19:36:11</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>62500</t>
+          <t>28395.06</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1629,12 +1629,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07/13 12:08:35</t>
+          <t>07/13 13:36:47</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>175000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1644,12 +1644,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>21341.46</t>
+          <t>62500</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1671,12 +1671,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07/13 10:45:12</t>
+          <t>07/13 12:08:35</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>600000</t>
+          <t>175000</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1686,12 +1686,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>21341.46</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1713,12 +1713,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07/12 14:43:07</t>
+          <t>07/13 10:45:12</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>600000</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1728,12 +1728,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>18404.91</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1755,12 +1755,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07/10 14:54:56</t>
+          <t>07/12 14:43:07</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>36809.82</t>
+          <t>18404.91</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1797,12 +1797,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07/10 13:44:44</t>
+          <t>07/10 14:54:56</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>36809.82</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1839,12 +1839,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07/10 13:24:33</t>
+          <t>07/10 13:44:44</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1854,12 +1854,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>29543.18</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1881,12 +1881,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07/09 20:44:16</t>
+          <t>07/10 13:24:33</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>12048.19</t>
+          <t>29543.18</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -1923,7 +1923,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07/09 09:52:57</t>
+          <t>07/09 20:44:16</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1965,12 +1965,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07/09 09:52:18</t>
+          <t>07/09 09:52:57</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>370000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1980,12 +1980,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>45962.73</t>
+          <t>12048.19</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2007,12 +2007,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07/09 09:51:15</t>
+          <t>07/09 09:52:18</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>370000</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>6172.84</t>
+          <t>45962.73</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2049,12 +2049,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07/08 11:55:35</t>
+          <t>07/09 09:51:15</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1000000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>124223.6</t>
+          <t>6172.84</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2091,12 +2091,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07/08 11:27:56</t>
+          <t>07/08 11:55:35</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>1000000</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2106,12 +2106,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>23952.1</t>
+          <t>124223.6</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2133,12 +2133,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07/07 17:03:42</t>
+          <t>07/08 11:27:56</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>23952.1</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2175,12 +2175,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07/07 12:04:13</t>
+          <t>07/07 17:03:42</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>6134.97</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2217,12 +2217,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07/07 10:57:24</t>
+          <t>07/07 12:04:13</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>60240.96</t>
+          <t>6134.97</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2259,12 +2259,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07/06 16:38:27</t>
+          <t>07/07 10:57:24</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2274,12 +2274,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>60240.96</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2301,12 +2301,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07/03 20:29:40</t>
+          <t>07/06 16:38:27</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2316,39 +2316,39 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>上海浦东新区 明天上午11</t>
+          <t/>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>17万 问</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07/03 13:13:45</t>
+          <t>07/03 20:29:40</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>325000</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2358,39 +2358,39 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>41139.24</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t/>
+          <t>上海浦东新区 明天上午11</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t/>
+          <t>17万 问</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07/02 15:46:17</t>
+          <t>07/03 13:13:45</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1064400</t>
+          <t>325000</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2400,12 +2400,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>133050</t>
+          <t>41139.24</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2427,12 +2427,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07/02 09:58:18</t>
+          <t>07/02 15:46:17</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>1064400</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>12422.36</t>
+          <t>133050</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2469,12 +2469,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07/02 09:16:59</t>
+          <t>07/02 09:58:18</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>230000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>28750</t>
+          <t>12422.36</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2511,12 +2511,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07/01 18:40:58</t>
+          <t>07/02 09:16:59</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>230000</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>28750</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
+          <t/>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>yxhgq52</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -2553,12 +2553,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07/01 15:38:21</t>
+          <t>07/01 18:40:58</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>250000</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>31250</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t/>
+          <t>:安徽省阜阳市临泉县杨桥镇 21 万明天 9.00</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -2595,12 +2595,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07/01 14:50:08</t>
+          <t>07/01 15:38:21</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>390000</t>
+          <t>250000</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>48148.15</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2637,12 +2637,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07/01 11:37:27</t>
+          <t>07/01 14:50:08</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>390000</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2652,12 +2652,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>12195.12</t>
+          <t>48148.15</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2679,12 +2679,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>06/30 18:54:28</t>
+          <t>07/01 11:37:27</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>12195.12</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2721,12 +2721,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>06/30 14:51:25</t>
+          <t>06/30 18:54:28</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>150000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>18518.52</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2763,12 +2763,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>06/30 14:28:35</t>
+          <t>06/30 14:51:25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>150000</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>12269.94</t>
+          <t>18518.52</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2805,12 +2805,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>06/30 13:54:27</t>
+          <t>06/30 14:28:35</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2820,12 +2820,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>12269.94</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2847,12 +2847,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>06/30 12:59:36</t>
+          <t>06/30 13:54:27</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>39751.55</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2889,12 +2889,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>06/30 10:46:18</t>
+          <t>06/30 12:59:36</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>34567.9</t>
+          <t>39751.55</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2931,12 +2931,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>06/30 10:21:46</t>
+          <t>06/30 10:46:18</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>940000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2946,12 +2946,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>117500</t>
+          <t>34567.9</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2973,12 +2973,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>06/30 10:05:33</t>
+          <t>06/30 10:21:46</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>500000</t>
+          <t>940000</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>62111.8</t>
+          <t>117500</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3015,12 +3015,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>06/29 12:46:01</t>
+          <t>06/30 10:05:33</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>24844.72</t>
+          <t>62111.8</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3057,12 +3057,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>06/27 11:40:49</t>
+          <t>06/29 12:46:01</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>37267.08</t>
+          <t>24844.72</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3099,12 +3099,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>06/26 14:39:57</t>
+          <t>06/27 11:40:49</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3114,12 +3114,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>12345.68</t>
+          <t>37267.08</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3141,12 +3141,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>06/26 10:00:12</t>
+          <t>06/26 14:39:57</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>160000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>19753.09</t>
+          <t>12345.68</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3183,12 +3183,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>06/26 08:47:43</t>
+          <t>06/26 10:00:12</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>160000</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>37037.04</t>
+          <t>19753.09</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3225,12 +3225,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>06/25 16:32:57</t>
+          <t>06/26 08:47:43</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>400000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3245,7 +3245,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>49382.72</t>
+          <t>37037.04</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3267,12 +3267,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>06/25 13:05:59</t>
+          <t>06/25 16:32:57</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>400000</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>39506.17</t>
+          <t>49382.72</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3309,12 +3309,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>06/24 12:43:07</t>
+          <t>06/25 13:05:59</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>35714.29</t>
+          <t>39506.17</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3351,12 +3351,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>06/24 12:35:27</t>
+          <t>06/24 12:43:07</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>180000</t>
+          <t>300000</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3366,12 +3366,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>22085.89</t>
+          <t>35714.29</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3393,12 +3393,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>06/24 12:06:55</t>
+          <t>06/24 12:35:27</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>180000</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>24691.36</t>
+          <t>22085.89</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3435,166 +3435,181 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
+          <t>06/24 12:06:55</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>24691.36</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
           <t>06/23 18:37:21</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B86" t="inlineStr">
         <is>
           <t>320000</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
         <is>
           <t>8.1</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="E86" t="inlineStr">
         <is>
           <t>39506.17</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="86"/>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="87"/>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="D89" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="E89" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="H89" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="89"/>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="90"/>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>07/26 12:04:42</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>07/20 14:01:29</t>
+          <t>07/26 12:04:42</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3616,12 +3631,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>07/07 12:04:32</t>
+          <t>07/20 14:01:29</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>438</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3643,12 +3658,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>06/30 14:52:47</t>
+          <t>07/07 12:04:32</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>276</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3670,12 +3685,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>06/30 10:52:45</t>
+          <t>06/30 14:52:47</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3697,83 +3712,110 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
+          <t>06/30 10:52:45</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="B98" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="98"/>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="99"/>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>20909140</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2589512.97</t>
+          <t>21129140</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>1928</t>
+          <t>2615243.96</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>1928</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>2587584.97</t>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2613315.96</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
+++ b/bills/JXZFSP01/-4684477615/d2a2b39eebccdff4256d863198fd6613e54ddc239f40982774b9f80b2bfe49e8/bill-all.xlsx
@@ -3604,12 +3604,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>07/26 12:04:42</t>
+          <t>09/15 13:27:56</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>25730</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3619,7 +3619,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>yxhgq52</t>
+          <t>yxhgq79</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -3631,12 +3631,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>07/20 14:01:29</t>
+          <t>07/26 12:04:42</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3658,12 +3658,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>07/07 12:04:32</t>
+          <t>07/20 14:01:29</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>276</t>
+          <t>438</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3685,12 +3685,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>06/30 14:52:47</t>
+          <t>07/07 12:04:32</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>276</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3712,12 +3712,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>06/30 10:52:45</t>
+          <t>06/30 14:52:47</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>188</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3739,83 +3739,110 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
+          <t>06/30 10:52:45</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
           <t>06/24 12:43:13</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B99" t="inlineStr">
         <is>
           <t>588</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>yxhgq52</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="99"/>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>yxhgq52</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="100"/>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>21129140</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2615243.96</t>
+          <t>21129140</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>1928</t>
+          <t>2615243.96</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>27658</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>2613315.96</t>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2587585.96</t>
         </is>
       </c>
     </row>
